--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -484,7 +484,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Administrator (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Administrator (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sells a ticket for a chosen show and seat, calculates the price automatically and marks the seat as unavailable.</t>
+          <t>Sells a ticket for a chosen show and seat, calculates the price automatically and marks the seat as unavailable. The customer provides details and receives the ticket.</t>
         </is>
       </c>
     </row>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Administrator, Cashier</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Administrator, Cashier</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Administrator (primary), Customer (secondary)</t>
+          <t>Cashier (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Administrator (primary), Customer (secondary)</t>
+          <t>Cashier (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Administrator, Cashier</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Authenticates the administrator before granting access to the dashboard.</t>
+          <t>Authenticates the user and opens the dashboard according to the role (ADMIN or CASHIER).</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Application running; a valid admin account exists.</t>
+          <t>Application running; a valid account exists in the users table.</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Administrator authenticated; dashboard opens.</t>
+          <t>User authenticated; dashboard opens with role-based access.</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1. Enter username and password. 2. System validates against the database. 3. On success, dashboard opens.</t>
+          <t>1. Enter username and password. 2. System validates against the users table and reads the role. 3. On success, dashboard opens (full menu for ADMIN, ticket menu for CASHIER).</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1349,7 +1349,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>admin_user</t>
+          <t>users</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -1398,7 +1398,11 @@
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1408,74 +1412,78 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(255)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>movie</t>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('ADMIN','CASHIER')</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>default 'CASHIER'</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Key / Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>movie_id</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr"/>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>genre</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr"/>
@@ -1483,12 +1491,12 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>duration_min</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr"/>
@@ -1496,7 +1504,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>cinema_hall</t>
+          <t>movie</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1528,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>hall_id</t>
+          <t>movie_id</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1537,222 +1545,226 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>hall_name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr"/>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>seating_capacity</t>
+          <t>genre</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>movie_show</t>
-        </is>
-      </c>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>cinema_hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Key / Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>show_id</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>movie_id</t>
+          <t>hall_id</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>FK -&gt; movie</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>hall_id</t>
+          <t>hall_name</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(60)</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>FK -&gt; cinema_hall</t>
+          <t>UQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>show_date</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>show_time</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>movie_show</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>pricing</t>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Key / Note</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Key / Note</t>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>pricing_id</t>
+          <t>movie_id</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK -&gt; movie</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>day_type</t>
+          <t>hall_id</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Weekday/Weekend</t>
+          <t>FK -&gt; cinema_hall</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>show_date</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Adult/Kid</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>show_time</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>DECIMAL(8,2)</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr"/>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>UQ(hall_id,date,time)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ticket</t>
+          <t>pricing_config</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1788,12 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>ticket_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -1793,29 +1805,25 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>show_id</t>
+          <t>weekday_adult</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; movie_show</t>
-        </is>
-      </c>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>seat_number</t>
+          <t>weekday_kid</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr"/>
@@ -1823,29 +1831,25 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>ticket_type</t>
+          <t>weekend_adult</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Adult/Kid</t>
-        </is>
-      </c>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>weekend_kid</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>DECIMAL(8,2)</t>
+          <t>INT(11)</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr"/>
@@ -1853,37 +1857,249 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>default CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Key / Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>ticket_id</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; movie_show</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>seat_number</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>UQ(show_id,seat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>ticket_type</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Adult','Kid')</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(10,2)</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>purchase_date</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr"/>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>default CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>show_details</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Key / Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>details_id</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>INT(11)</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>UQ -&gt; movie_show</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>movie_name</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>hall_name</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(60)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A28:C28"/>
+  <mergeCells count="8">
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A54:C54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -479,12 +479,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Administrator, Cashier</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Administrator, Cashier</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Update Cinema Hall</t>
+          <t>View Cinema Halls</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Delete Cinema Hall</t>
+          <t>Add Movie Show</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>View Cinema Halls</t>
+          <t>Update Movie Show</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Add Movie Show</t>
+          <t>Delete Movie Show</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Update Movie Show</t>
+          <t>View / Search Movie Shows</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Delete Movie Show</t>
+          <t>Book Ticket</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Administrator (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>View Movie Shows</t>
+          <t>Cancel Ticket</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Update Ticket Pricing (Weekday/Weekend - Adult/Kid)</t>
+          <t>View Sold Tickets</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -742,117 +742,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>View Ticket Pricing</t>
+          <t>Generate Sales Report</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Book Ticket (Sell Ticket)</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Cashier (primary), Customer (secondary)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Select Seat</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Check Seat Availability</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Calculate Ticket Price</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>View Sold Tickets</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Update Ticket</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Cancel / Delete Ticket</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Cashier</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -880,7 +775,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>UC-17  —  Book Ticket (Sell Ticket)</t>
+          <t>UC-13  —  Book Ticket</t>
         </is>
       </c>
       <c r="B1" s="4" t="n"/>
@@ -893,7 +788,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>UC-17</t>
+          <t>UC-13</t>
         </is>
       </c>
     </row>
@@ -905,7 +800,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Book Ticket (Sell Ticket)</t>
+          <t>Book Ticket</t>
         </is>
       </c>
     </row>
@@ -917,7 +812,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cashier (primary), Customer (secondary)</t>
+          <t>Administrator (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -929,7 +824,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sells a ticket for a chosen show and seat, calculates the price automatically and marks the seat as unavailable. The customer provides details and receives the ticket.</t>
+          <t>Sells a ticket for a chosen show and seat, records the customer and marks the seat as sold.</t>
         </is>
       </c>
     </row>
@@ -941,7 +836,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Administrator is logged in; a show with a free seat exists; pricing is configured.</t>
+          <t>Administrator is logged in; a show with a free seat exists.</t>
         </is>
       </c>
     </row>
@@ -953,7 +848,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A ticket record is saved; the chosen seat becomes unavailable.</t>
+          <t>A ticket is saved against the show and customer; the seat becomes unavailable.</t>
         </is>
       </c>
     </row>
@@ -965,7 +860,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1. Select a movie show. 2. Select a seat (include Select Seat). 3. Check seat is free (include Check Seat Availability). 4. Enter customer details and ticket type (Adult/Kid). 5. System calculates price from pricing rules (include Calculate Ticket Price). 6. Confirm; save ticket and mark seat sold. 7. Show confirmation.</t>
+          <t>1. Select a movie show. 2. Select a seat number. 3. Check seat is free (include Check Seat Availability). 4. Enter customer name and phone. 5. Read show ticket price (include Calculate Ticket Price). 6. Confirm; save ticket and mark seat sold. 7. Show confirmation.</t>
         </is>
       </c>
     </row>
@@ -977,7 +872,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3a. Seat already sold -&gt; ask for another seat. 4a. Invalid/missing input -&gt; validation error, not saved.</t>
+          <t>3a. Seat already sold -&gt; ask for another seat. 4a. Missing details -&gt; validation error, not saved.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +920,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Administrator, Cashier</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -1037,7 +932,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Authenticates the user and opens the dashboard according to the role (ADMIN or CASHIER).</t>
+          <t>Authenticates the administrator before granting access to the system.</t>
         </is>
       </c>
     </row>
@@ -1049,7 +944,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Application running; a valid account exists in the users table.</t>
+          <t>Application running; a valid account exists.</t>
         </is>
       </c>
     </row>
@@ -1061,7 +956,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>User authenticated; dashboard opens with role-based access.</t>
+          <t>Administrator authenticated; main menu opens.</t>
         </is>
       </c>
     </row>
@@ -1073,7 +968,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1. Enter username and password. 2. System validates against the users table and reads the role. 3. On success, dashboard opens (full menu for ADMIN, ticket menu for CASHIER).</t>
+          <t>1. Enter username and password. 2. System validates against the database. 3. On success, main menu opens.</t>
         </is>
       </c>
     </row>
@@ -1096,7 +991,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>UC-15  —  Update Ticket Pricing</t>
+          <t>UC-09  —  Add Movie Show</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1109,7 +1004,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>UC-15</t>
+          <t>UC-09</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1016,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Update Ticket Pricing</t>
+          <t>Add Movie Show</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1040,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Updates ticket prices that vary by day type (weekday/weekend) and category (adult/kid), without changing code.</t>
+          <t>Schedules a movie in a hall at a given date, time and ticket price.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1052,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Administrator is logged in.</t>
+          <t>Administrator is logged in; at least one movie and one hall exist.</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1064,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>New prices stored and used automatically by the booking screen.</t>
+          <t>A new show record is stored.</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1076,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>1. Open Pricing Management. 2. System shows current prices. 3. Edit prices and save. 4. Store new prices; bookings use them automatically.</t>
+          <t>1. Open Show Management. 2. Choose movie and hall, enter date, time, ticket price. 3. Click Add. 4. Validate and save, refresh table.</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1088,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>3a. Invalid numeric input -&gt; validation error, prices unchanged.</t>
+          <t>3a. A show already exists for that hall at that date/time -&gt; duplicate error.</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1211,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Replicate this template for the remaining CRUD use cases (Update/Delete/View of Movie, Hall, Show; View Pricing; View/Update/Cancel Ticket; Logout).</t>
+          <t>Replicate this template for: Update/Delete/View Movie, Add/View Hall, Update/Delete/View Show, Cancel Ticket, View Sold Tickets, Generate Sales Report, Logout.</t>
         </is>
       </c>
     </row>
@@ -1338,18 +1233,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>users</t>
+          <t>user</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1261,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Key / Note</t>
+          <t>Key</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1273,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>INT (auto)</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -1398,11 +1293,7 @@
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="C4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1417,73 +1308,69 @@
       </c>
       <c r="C5" s="9" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>ENUM('ADMIN','CASHIER')</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>default 'CASHIER'</t>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>movie</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>customer</t>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Key / Note</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>genre</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr"/>
@@ -1491,12 +1378,12 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr"/>
@@ -1504,7 +1391,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>movie</t>
+          <t>cinema_hall</t>
         </is>
       </c>
     </row>
@@ -1521,19 +1408,19 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Key / Note</t>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>movie_id</t>
+          <t>hall_id</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>INT (auto)</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1545,201 +1432,193 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>hall_name</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(120)</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+          <t>VARCHAR(60)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>genre</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>movie_show</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>cinema_hall</t>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Key / Note</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>hall_id</t>
+          <t>movie_id</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK -&gt; movie</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>hall_name</t>
+          <t>hall_id</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(60)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>FK -&gt; cinema_hall</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>show_date</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>show_time</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>movie_show</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>ticket_price</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>Key / Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>show_id</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>movie_id</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; movie</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>hall_id</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>INT (auto)</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>FK -&gt; cinema_hall</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>show_date</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr"/>
@@ -1747,24 +1626,20 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>show_time</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>UQ(hall_id,date,time)</t>
-        </is>
-      </c>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>pricing_config</t>
+          <t>ticket</t>
         </is>
       </c>
     </row>
@@ -1781,19 +1656,19 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Key / Note</t>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ticket_id</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>INT (auto)</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -1805,38 +1680,46 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>weekday_adult</t>
+          <t>show_id</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; movie_show</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>weekday_kid</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; customer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>weekend_adult</t>
+          <t>seat_number</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr"/>
@@ -1844,12 +1727,12 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>weekend_kid</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>INT(11)</t>
+          <t>DECIMAL(8,2)</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr"/>
@@ -1857,249 +1740,24 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>purchase_date</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>default CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>ticket</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Key / Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>ticket_id</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>show_id</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; movie_show</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>seat_number</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>UQ(show_id,seat)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>ticket_type</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>ENUM('Adult','Kid')</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>DECIMAL(10,2)</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>purchase_date</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>default CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>show_details</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>Key / Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>details_id</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>show_id</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>INT(11)</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>UQ -&gt; movie_show</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>movie_name</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(120)</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>hall_name</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(60)</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr"/>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A44:C44"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A20:C20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -479,12 +479,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -517,12 +517,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Register Account</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier, Manager</t>
         </is>
       </c>
     </row>
@@ -547,12 +547,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Add Movie</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier, Manager</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Update Movie</t>
+          <t>Search / Browse Movies</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Delete Movie</t>
+          <t>View Showtimes</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>View / Search Movies</t>
+          <t>Book Ticket</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Add Cinema Hall</t>
+          <t>Select Seats</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>View Cinema Halls</t>
+          <t>Make Payment</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier</t>
         </is>
       </c>
     </row>
@@ -637,12 +637,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Add Movie Show</t>
+          <t>View My Bookings</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Update Movie Show</t>
+          <t>Cancel Booking</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier</t>
         </is>
       </c>
     </row>
@@ -667,12 +667,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Delete Movie Show</t>
+          <t>Validate Ticket at Entrance</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>View / Search Movie Shows</t>
+          <t>Add Movie</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -697,12 +697,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Book Ticket</t>
+          <t>Update Movie</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Administrator (primary), Customer (secondary)</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Cancel Ticket</t>
+          <t>Delete Movie</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>View Sold Tickets</t>
+          <t>Schedule Showtime</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,72 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Generate Sales Report</t>
+          <t>Update Showtime</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Delete Showtime</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Manage Cinema Halls</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Set Ticket Pricing</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>View Sales Report</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -769,13 +829,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>UC-13  —  Book Ticket</t>
+          <t>UC-06  —  Book Ticket</t>
         </is>
       </c>
       <c r="B1" s="4" t="n"/>
@@ -788,7 +848,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>UC-13</t>
+          <t>UC-06</t>
         </is>
       </c>
     </row>
@@ -812,7 +872,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Administrator (primary), Customer (secondary)</t>
+          <t>Customer (online), Cashier (counter)</t>
         </is>
       </c>
     </row>
@@ -824,7 +884,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sells a ticket for a chosen show and seat, records the customer and marks the seat as sold.</t>
+          <t>Reserves one or more seats for a showtime, takes payment and issues a ticket.</t>
         </is>
       </c>
     </row>
@@ -836,7 +896,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Administrator is logged in; a show with a free seat exists.</t>
+          <t>Actor is logged in; a showtime with at least one free seat exists.</t>
         </is>
       </c>
     </row>
@@ -848,7 +908,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A ticket is saved against the show and customer; the seat becomes unavailable.</t>
+          <t>A booking and ticket are saved; the chosen seats are marked sold.</t>
         </is>
       </c>
     </row>
@@ -860,7 +920,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1. Select a movie show. 2. Select a seat number. 3. Check seat is free (include Check Seat Availability). 4. Enter customer name and phone. 5. Read show ticket price (include Calculate Ticket Price). 6. Confirm; save ticket and mark seat sold. 7. Show confirmation.</t>
+          <t>1. Select a movie and showtime. 2. System shows the seat map. 3. Select seats (include Select Seats). 4. System reserves seats and shows total. 5. Confirm and pay (include Make Payment). 6. On success, save booking, issue ticket(s), mark seats sold. 7. Show ticket with reference.</t>
         </is>
       </c>
     </row>
@@ -872,7 +932,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3a. Seat already sold -&gt; ask for another seat. 4a. Missing details -&gt; validation error, not saved.</t>
+          <t>3a. Seat taken meanwhile -&gt; choose another seat. 5a. Payment fails -&gt; release seats, error, no ticket.</t>
         </is>
       </c>
     </row>
@@ -883,7 +943,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>UC-01  —  Login</t>
+          <t>UC-08  —  Make Payment</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -896,7 +956,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>UC-01</t>
+          <t>UC-08</t>
         </is>
       </c>
     </row>
@@ -908,7 +968,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Make Payment</t>
         </is>
       </c>
     </row>
@@ -920,7 +980,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Customer, Cashier</t>
         </is>
       </c>
     </row>
@@ -932,7 +992,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Authenticates the administrator before granting access to the system.</t>
+          <t>Charges the customer for a booking.</t>
         </is>
       </c>
     </row>
@@ -944,7 +1004,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Application running; a valid account exists.</t>
+          <t>A booking with a total amount is awaiting payment.</t>
         </is>
       </c>
     </row>
@@ -956,7 +1016,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Administrator authenticated; main menu opens.</t>
+          <t>A payment record is created with status Paid or Failed.</t>
         </is>
       </c>
     </row>
@@ -968,7 +1028,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1. Enter username and password. 2. System validates against the database. 3. On success, main menu opens.</t>
+          <t>1. Show amount due and methods (Card, Mobile Money, Cash). 2. Choose method, enter details. 3. Process payment, record as Paid.</t>
         </is>
       </c>
     </row>
@@ -980,7 +1040,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2a. Invalid credentials -&gt; show 'Invalid login credentials', stay on login screen.</t>
+          <t>3a. Declined -&gt; record Failed, notify; booking stays unpaid.</t>
         </is>
       </c>
     </row>
@@ -991,7 +1051,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>UC-09  —  Add Movie Show</t>
+          <t>UC-15  —  Schedule Showtime</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1004,7 +1064,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>UC-09</t>
+          <t>UC-15</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1076,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Add Movie Show</t>
+          <t>Schedule Showtime</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1088,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1112,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Administrator is logged in; at least one movie and one hall exist.</t>
+          <t>Manager is logged in; at least one movie and one hall exist.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1124,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>A new show record is stored.</t>
+          <t>A new showtime is stored.</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1136,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>1. Open Show Management. 2. Choose movie and hall, enter date, time, ticket price. 3. Click Add. 4. Validate and save, refresh table.</t>
+          <t>1. Open Showtime scheduling. 2. Choose movie and hall, enter date, time, ticket price. 3. Save. 4. Validate and store the showtime.</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1148,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>3a. A show already exists for that hall at that date/time -&gt; duplicate error.</t>
+          <t>3a. A showtime already exists for that hall at that date/time -&gt; clash error.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1159,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>UC-03  —  Add Movie</t>
+          <t>UC-12  —  Add Movie</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1112,7 +1172,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>UC-03</t>
+          <t>UC-12</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1196,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1220,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Administrator is logged in.</t>
+          <t>Manager is logged in.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1244,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>1. Open Movie Management. 2. Enter title, genre, duration. 3. Click Add. 4. Validate and save, refresh table.</t>
+          <t>1. Open Movie Management. 2. Enter title, genre, duration, language, rating. 3. Save. 4. Validate and store the movie.</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1271,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Replicate this template for: Update/Delete/View Movie, Add/View Hall, Update/Delete/View Show, Cancel Ticket, View Sold Tickets, Generate Sales Report, Logout.</t>
+          <t>Replicate this template for: Update/Delete Movie, Update/Delete Showtime, Manage Cinema Halls, Set Ticket Pricing, Register Account, View My Bookings, Cancel Booking, Validate Ticket, View Sales Report, Logout.</t>
         </is>
       </c>
     </row>
@@ -1233,18 +1293,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>customer</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1328,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -1285,12 +1345,12 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr"/>
@@ -1298,466 +1358,740 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
           <t>password</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>movie</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>movie_id</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(120)</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>genre</t>
+          <t>staff_id</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr"/>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>full_name</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr"/>
+    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>cinema_hall</t>
-        </is>
-      </c>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('MANAGER','CASHIER')</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>hall_id</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>INT (auto)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>hall_name</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(60)</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>movie_show</t>
-        </is>
-      </c>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>genre</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>show_id</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>movie_id</t>
+          <t>language</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; movie</t>
-        </is>
-      </c>
+          <t>VARCHAR(40)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>cinema_hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
           <t>hall_id</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>hall_name</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(60)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>hall_id</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>FK -&gt; cinema_hall</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>show_date</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>show_time</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>ticket_price</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>DECIMAL(8,2)</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>full_name</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>ticket</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>ticket_id</t>
+          <t>show_date</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>show_id</t>
+          <t>show_time</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; movie_show</t>
-        </is>
-      </c>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
+          <t>ticket_price</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>FK -&gt; customer</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>booking_datetime</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Paid','Cancelled','Pending')</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>ticket_id</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>seat_number</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(8)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>payment_id</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>purchase_date</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Card','MobileMoney','Cash')</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>payment_datetime</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr"/>
+      <c r="C63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Paid','Failed')</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -483,8 +483,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -517,12 +517,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Register Account</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Manager, Cashier</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier, Manager</t>
+          <t>Manager, Cashier</t>
         </is>
       </c>
     </row>
@@ -547,12 +547,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Search / View Movies</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier, Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Search / Browse Movies</t>
+          <t>View Showtimes</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>View Showtimes</t>
+          <t>Sell Ticket</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier</t>
+          <t>Cashier (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Book Ticket</t>
+          <t>Select Seat</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Select Seats</t>
+          <t>Check Seat Availability</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Make Payment</t>
+          <t>Take Payment</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -637,12 +637,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>View My Bookings</t>
+          <t>Cancel Ticket</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cancel Booking</t>
+          <t>Validate Ticket at Entrance</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Validate Ticket at Entrance</t>
+          <t>View Sold Tickets</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Schedule Showtime</t>
+          <t>Manage Cinema Halls</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Update Showtime</t>
+          <t>Schedule Showtime</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Delete Showtime</t>
+          <t>Update Showtime</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Manage Cinema Halls</t>
+          <t>Delete Showtime</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>UC-06  —  Book Ticket</t>
+          <t>UC-05  —  Sell Ticket</t>
         </is>
       </c>
       <c r="B1" s="4" t="n"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>UC-06</t>
+          <t>UC-05</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Book Ticket</t>
+          <t>Sell Ticket</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Customer (online), Cashier (counter)</t>
+          <t>Cashier (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Reserves one or more seats for a showtime, takes payment and issues a ticket.</t>
+          <t>Sells a ticket for a chosen showtime and seat: records the customer, takes payment and marks the seat sold.</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Actor is logged in; a showtime with at least one free seat exists.</t>
+          <t>Cashier is logged in; a showtime with at least one free seat exists.</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A booking and ticket are saved; the chosen seats are marked sold.</t>
+          <t>A ticket is saved against the showtime and customer; the seat is marked sold.</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1. Select a movie and showtime. 2. System shows the seat map. 3. Select seats (include Select Seats). 4. System reserves seats and shows total. 5. Confirm and pay (include Make Payment). 6. On success, save booking, issue ticket(s), mark seats sold. 7. Show ticket with reference.</t>
+          <t>1. Select a movie and showtime. 2. Select a seat (include Select Seat). 3. Check seat is free (include Check Seat Availability). 4. Enter customer name, phone and ticket type (Adult/Kid). 5. Show price and take payment (include Take Payment). 6. Save ticket and mark seat sold. 7. Print/show the ticket.</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3a. Seat taken meanwhile -&gt; choose another seat. 5a. Payment fails -&gt; release seats, error, no ticket.</t>
+          <t>3a. Seat already sold -&gt; choose another seat. 5a. Payment not completed -&gt; release seat, no ticket. 4a. Missing details -&gt; validation error.</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>UC-08  —  Make Payment</t>
+          <t>UC-01  —  Login</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -956,7 +956,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>UC-08</t>
+          <t>UC-01</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Make Payment</t>
+          <t>Login</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Customer, Cashier</t>
+          <t>Manager, Cashier</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Charges the customer for a booking.</t>
+          <t>Authenticates a staff member and opens the menu according to their role.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>A booking with a total amount is awaiting payment.</t>
+          <t>Application running; a valid staff account exists.</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>A payment record is created with status Paid or Failed.</t>
+          <t>Staff authenticated with role-based access.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1. Show amount due and methods (Card, Mobile Money, Cash). 2. Choose method, enter details. 3. Process payment, record as Paid.</t>
+          <t>1. Enter username and password. 2. System validates and reads the role. 3. On success, the menu opens (full for Manager, selling for Cashier).</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>3a. Declined -&gt; record Failed, notify; booking stays unpaid.</t>
+          <t>2a. Invalid credentials -&gt; show 'Invalid login credentials', stay on login screen.</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>UC-15  —  Schedule Showtime</t>
+          <t>UC-16  —  Schedule Showtime</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>UC-15</t>
+          <t>UC-16</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>1. Open Movie Management. 2. Enter title, genre, duration, language, rating. 3. Save. 4. Validate and store the movie.</t>
+          <t>1. Open Movie Management. 2. Enter title, genre, duration, rating. 3. Save. 4. Validate and store.</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Replicate this template for: Update/Delete Movie, Update/Delete Showtime, Manage Cinema Halls, Set Ticket Pricing, Register Account, View My Bookings, Cancel Booking, Validate Ticket, View Sales Report, Logout.</t>
+          <t>Replicate this template for: Update/Delete Movie, Manage Cinema Halls, Update/Delete Showtime, Set Ticket Pricing, Search Movies, View Showtimes, Cancel Ticket, Validate Ticket, View Sold Tickets, View Sales Report, Logout.</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1304,7 +1304,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>customer</t>
+          <t>staff</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>staff_id</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -1358,25 +1358,29 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>username</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr"/>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>password</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr"/>
@@ -1384,12 +1388,12 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(255)</t>
+          <t>ENUM('MANAGER','CASHIER')</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
@@ -1397,7 +1401,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>customer</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1425,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>staff_id</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -1451,92 +1455,92 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>username</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>password</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(255)</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>ENUM('MANAGER','CASHIER')</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>movie</t>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>movie_id</t>
+          <t>genre</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(120)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr"/>
@@ -1544,315 +1548,323 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>genre</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>cinema_hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>hall_id</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>hall_name</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(60)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(40)</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>cinema_hall</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>hall_id</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>hall_name</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(60)</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>showtime</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; cinema_hall</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>show_id</t>
+          <t>show_date</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>movie_id</t>
+          <t>show_time</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>FK -&gt; movie</t>
+          <t>UQ(hall,date,time)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>hall_id</t>
+          <t>ticket_price</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>ticket_id</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; cinema_hall</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>show_date</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>show_time</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>ticket_price</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>DECIMAL(8,2)</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>booking</t>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; showtime</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; customer</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>booking_id</t>
+          <t>seat_number</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>VARCHAR(8)</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>UQ(show,seat)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>ticket_type</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; customer</t>
-        </is>
-      </c>
+          <t>ENUM('Adult','Kid')</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>show_id</t>
+          <t>price</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; showtime</t>
-        </is>
-      </c>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>booking_datetime</t>
+          <t>purchase_datetime</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -1862,236 +1874,14 @@
       </c>
       <c r="C46" s="9" t="inlineStr"/>
     </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>ENUM('Paid','Cancelled','Pending')</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>DECIMAL(8,2)</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>ticket</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>ticket_id</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>booking_id</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; booking</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>seat_number</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(8)</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>DECIMAL(8,2)</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>payment_id</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>booking_id</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; booking</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>DECIMAL(8,2)</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>ENUM('Card','MobileMoney','Cash')</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>payment_datetime</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>ENUM('Paid','Failed')</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A41:C41"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -110,7 +110,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -479,12 +481,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -517,12 +519,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Add Movie</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -532,12 +534,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>Update Movie</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -547,12 +549,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Search / View Movies</t>
+          <t>Delete Movie</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -562,12 +564,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>View Showtimes</t>
+          <t>Search Movie by Title, Genre, Language</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager, Cashier</t>
         </is>
       </c>
     </row>
@@ -577,12 +579,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sell Ticket</t>
+          <t>Add Genre</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Cashier (primary), Customer (secondary)</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -592,12 +594,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Select Seat</t>
+          <t>Update Genre</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -607,12 +609,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Check Seat Availability</t>
+          <t>Delete Genre</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -622,12 +624,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Take Payment</t>
+          <t>Search Genre by Name</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -637,12 +639,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Cancel Ticket</t>
+          <t>Add Cinema Hall</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -652,12 +654,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Validate Ticket at Entrance</t>
+          <t>Update Cinema Hall</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -667,12 +669,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>View Sold Tickets</t>
+          <t>Delete Cinema Hall</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -682,7 +684,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Add Movie</t>
+          <t>Search Cinema Hall by Name, Type, Capacity</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -697,7 +699,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Update Movie</t>
+          <t>Add Showtime</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -712,7 +714,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Delete Movie</t>
+          <t>Update Showtime</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -727,7 +729,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Manage Cinema Halls</t>
+          <t>Delete Showtime</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -742,12 +744,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Schedule Showtime</t>
+          <t>Search Showtime by Date, Movie, Hall, Time</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Manager, Cashier</t>
         </is>
       </c>
     </row>
@@ -757,12 +759,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Update Showtime</t>
+          <t>Add Customer</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -772,12 +774,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Delete Showtime</t>
+          <t>Update Customer</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -787,7 +789,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Set Ticket Pricing</t>
+          <t>Delete Customer</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -802,12 +804,567 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>View Sales Report</t>
+          <t>Search Customer by Id, Name, Phone</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Add Staff</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Update Staff</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Delete Staff</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Search Staff by Id, Name, Role</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Add Booking</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Customer (secondary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Update Booking</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Delete Booking</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Search Booking by Id, Customer, Date, Showtime</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Add Ticket</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Update Ticket</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Delete Ticket</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Search Ticket by Code, Showtime, Customer</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Usher</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Add Payment</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Update Payment</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Delete Payment</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Search Payment by Id, Date, Method, Customer</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Add Snack</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Update Snack</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Delete Snack</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Search Snack by Name, Category</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Add Promotion</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Update Promotion</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Delete Promotion</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Search Promotion by Code, Period</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Post Showtime</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Unpost Showtime</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Select Seat</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Customer (secondary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Apply Promotion to Booking</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Generate Ticket</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Validate Ticket at Entrance</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Usher</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Issue Refund</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Cashier, Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Generate Sales Report</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Generate Hall Occupancy Report</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Generate Daily Revenue Report</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Manage User Roles</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Manager, Cashier, Usher</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Manager, Cashier, Usher</t>
         </is>
       </c>
     </row>
@@ -829,13 +1386,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>UC-05  —  Sell Ticket</t>
+          <t>UC-25  —  Add Booking</t>
         </is>
       </c>
       <c r="B1" s="4" t="n"/>
@@ -848,7 +1405,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>UC-05</t>
+          <t>UC-25</t>
         </is>
       </c>
     </row>
@@ -860,7 +1417,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Sell Ticket</t>
+          <t>Add Booking</t>
         </is>
       </c>
     </row>
@@ -884,7 +1441,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sells a ticket for a chosen showtime and seat: records the customer, takes payment and marks the seat sold.</t>
+          <t>Creates a booking for a showtime: selects seats, applies any promotion, takes payment and issues the ticket.</t>
         </is>
       </c>
     </row>
@@ -896,7 +1453,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cashier is logged in; a showtime with at least one free seat exists.</t>
+          <t>Cashier is logged in; a posted showtime with a free seat exists.</t>
         </is>
       </c>
     </row>
@@ -908,7 +1465,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A ticket is saved against the showtime and customer; the seat is marked sold.</t>
+          <t>A booking, ticket and payment are saved; the seats are marked sold.</t>
         </is>
       </c>
     </row>
@@ -920,7 +1477,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1. Select a movie and showtime. 2. Select a seat (include Select Seat). 3. Check seat is free (include Check Seat Availability). 4. Enter customer name, phone and ticket type (Adult/Kid). 5. Show price and take payment (include Take Payment). 6. Save ticket and mark seat sold. 7. Print/show the ticket.</t>
+          <t>1. Select a posted showtime. 2. Select seats (include Select Seat). 3. Enter/select the customer. 4. (optional) Apply a promotion (extend Apply Promotion). 5. Show total and take payment (include Add Payment). 6. Save booking and issue ticket (include Generate Ticket); mark seats sold.</t>
         </is>
       </c>
     </row>
@@ -932,7 +1489,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3a. Seat already sold -&gt; choose another seat. 5a. Payment not completed -&gt; release seat, no ticket. 4a. Missing details -&gt; validation error.</t>
+          <t>2a. Seat already sold -&gt; choose another seat. 5a. Payment fails -&gt; release seats, no ticket.</t>
         </is>
       </c>
     </row>
@@ -943,7 +1500,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>UC-01  —  Login</t>
+          <t>UC-50  —  Validate Ticket at Entrance</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -956,7 +1513,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>UC-01</t>
+          <t>UC-50</t>
         </is>
       </c>
     </row>
@@ -968,7 +1525,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Validate Ticket at Entrance</t>
         </is>
       </c>
     </row>
@@ -980,7 +1537,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier</t>
+          <t>Usher</t>
         </is>
       </c>
     </row>
@@ -992,7 +1549,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Authenticates a staff member and opens the menu according to their role.</t>
+          <t>Checks a presented ticket is valid for the current showtime and marks it used.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1561,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Application running; a valid staff account exists.</t>
+          <t>Usher is logged in; the ticket exists.</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1573,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Staff authenticated with role-based access.</t>
+          <t>Ticket marked Used; entry granted or refused.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1585,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1. Enter username and password. 2. System validates and reads the role. 3. On success, the menu opens (full for Manager, selling for Cashier).</t>
+          <t>1. Scan/enter the ticket code. 2. Find ticket and showtime. 3. Check valid, right showtime, not used. 4. Mark Used and show 'Access granted'.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1597,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2a. Invalid credentials -&gt; show 'Invalid login credentials', stay on login screen.</t>
+          <t>3a. Already used / wrong showtime -&gt; 'Invalid ticket', refuse entry.</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1608,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>UC-16  —  Schedule Showtime</t>
+          <t>UC-52  —  Generate Sales Report</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1064,7 +1621,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>UC-16</t>
+          <t>UC-52</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1633,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Schedule Showtime</t>
+          <t>Generate Sales Report</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1657,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Schedules a movie in a hall at a given date, time and ticket price.</t>
+          <t>Produces a report of tickets sold and revenue for a chosen period.</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1669,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Manager is logged in; at least one movie and one hall exist.</t>
+          <t>Manager is logged in.</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1681,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>A new showtime is stored.</t>
+          <t>A report is displayed/printed.</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1693,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>1. Open Showtime scheduling. 2. Choose movie and hall, enter date, time, ticket price. 3. Save. 4. Validate and store the showtime.</t>
+          <t>1. Choose the period (date range). 2. System totals tickets sold and revenue. 3. Display report with grand total.</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1705,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>3a. A showtime already exists for that hall at that date/time -&gt; clash error.</t>
+          <t>1a. No data in period -&gt; report shows zero totals.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1716,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>UC-12  —  Add Movie</t>
+          <t>UC-01  —  Add Movie</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1172,7 +1729,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>UC-12</t>
+          <t>UC-01</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1765,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Adds a new movie to the catalogue.</t>
+          <t>Adds a new movie to the catalogue (template for all Add/Update/Delete/Search use cases).</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1801,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>1. Open Movie Management. 2. Enter title, genre, duration, rating. 3. Save. 4. Validate and store.</t>
+          <t>1. Open the Movie form. 2. Enter title, genre, duration, language, rating. 3. Save. 4. Validate and store.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1813,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>3a. Duplicate title / missing field -&gt; error, not saved.</t>
+          <t>3a. Duplicate / missing field -&gt; error, not saved.</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1828,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Replicate this template for: Update/Delete Movie, Manage Cinema Halls, Update/Delete Showtime, Set Ticket Pricing, Search Movies, View Showtimes, Cancel Ticket, Validate Ticket, View Sold Tickets, View Sales Report, Logout.</t>
+          <t>Replicate the CRUD template for every Add/Update/Delete/Search use case of Movie, Genre, Hall, Showtime, Customer, Staff, Booking, Ticket, Payment, Snack, Promotion. Write full specs for Post/Unpost Showtime, Select Seat, Apply Promotion, Add Payment, Generate Ticket, Issue Refund, the three reports, Manage User Roles, Login, Logout.</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1850,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1366,11 +1923,7 @@
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
+      <c r="C5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -1393,7 +1946,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>ENUM('MANAGER','CASHIER')</t>
+          <t>ENUM('MANAGER','CASHIER','USHER')</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
@@ -1465,64 +2018,64 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>movie</t>
-        </is>
-      </c>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>movie_id</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>genre_id</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(120)</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr"/>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>genre</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1532,82 +2085,86 @@
       </c>
       <c r="C19" s="9" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>cinema_hall</t>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>movie_id</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>hall_id</t>
+          <t>genre_id</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK -&gt; genre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>hall_name</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(60)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr"/>
@@ -1615,100 +2172,92 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>language</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr"/>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>showtime</t>
-        </is>
-      </c>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>cinema_hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Key</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>show_id</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>INT (auto)</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>movie_id</t>
+          <t>hall_id</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>INT (auto)</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>FK -&gt; movie</t>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>hall_id</t>
+          <t>hall_name</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; cinema_hall</t>
-        </is>
-      </c>
+          <t>VARCHAR(60)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>show_date</t>
+          <t>hall_type</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr"/>
@@ -1716,78 +2265,78 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>show_time</t>
+          <t>capacity</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>UQ(hall,date,time)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>ticket_price</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>DECIMAL(8,2)</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>showtime</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>ticket</t>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Key</t>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>ticket_id</t>
+          <t>movie_id</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK -&gt; movie</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>show_id</t>
+          <t>hall_id</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1797,53 +2346,45 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>FK -&gt; showtime</t>
+          <t>FK -&gt; cinema_hall</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>show_date</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>FK -&gt; customer</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>seat_number</t>
+          <t>show_time</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>VARCHAR(8)</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>UQ(show,seat)</t>
-        </is>
-      </c>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>ticket_type</t>
+          <t>ticket_price</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>ENUM('Adult','Kid')</t>
+          <t>DECIMAL(8,2)</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr"/>
@@ -1851,37 +2392,655 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Posted','Unposted')</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>show_id</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>promotion_id</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; promotion (null)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>booking_datetime</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Confirmed','Cancelled')</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>ticket_id</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>seat_number</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(8)</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>purchase_datetime</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Valid','Used','Refunded')</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>payment_id</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Card','Mobile','Cash')</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>payment_datetime</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr"/>
+      <c r="C71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>ENUM('Paid','Refunded')</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>snack_id</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>snack_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>booking_id</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>snack_id</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>FK -&gt; snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>line_total</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(8,2)</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>promotion_id</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>INT (auto)</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>discount_percent</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>DECIMAL(5,2)</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A74:C74"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -989,7 +989,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Usher</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Usher</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier, Usher</t>
+          <t>Manager, Cashier</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier, Usher</t>
+          <t>Manager, Cashier</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Usher</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Usher is logged in; the ticket exists.</t>
+          <t>Cashier is logged in; the ticket exists.</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1. Scan/enter the ticket code. 2. Find ticket and showtime. 3. Check valid, right showtime, not used. 4. Mark Used and show 'Access granted'.</t>
+          <t>1. Scan/enter the ticket code. 2. Find ticket and showtime. 3. Check valid, right showtime, not used. 4. Mark Used and show 'Access granted' with the seat number.</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>ENUM('MANAGER','CASHIER','USHER')</t>
+          <t>ENUM('MANAGER','CASHIER')</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr"/>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Customer (secondary)</t>
+          <t>Cashier (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Customer (secondary)</t>
+          <t>Cashier (primary), Customer (secondary)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Cashier, Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Generate Daily Revenue Report</t>
+          <t>Manage User Roles</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Manage User Roles</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1344,27 +1344,12 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Manager, Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Logout</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Manager, Cashier</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1813,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Replicate the CRUD template for every Add/Update/Delete/Search use case of Movie, Genre, Hall, Showtime, Customer, Staff, Booking, Ticket, Payment, Snack, Promotion. Write full specs for Post/Unpost Showtime, Select Seat, Apply Promotion, Add Payment, Generate Ticket, Issue Refund, the three reports, Manage User Roles, Login, Logout.</t>
+          <t>Replicate the CRUD template for every Add/Update/Delete/Search use case of Movie, Genre, Hall, Showtime, Customer, Staff, Booking, Ticket, Payment, Snack, Promotion. Write full specs for Post/Unpost Showtime, Select Seat, Apply Promotion, Add Payment, Generate Ticket, Issue Refund, the two reports, Manage User Roles, Login, Logout.</t>
         </is>
       </c>
     </row>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Cashier (primary), Customer (secondary)</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -884,7 +884,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Cashier (primary), Customer (secondary)</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Cashier (primary), Customer (secondary)</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Creates a booking for a showtime: selects seats, applies any promotion, takes payment and issues the ticket.</t>
+          <t>The cashier creates a booking for a showtime on behalf of a customer: selects seats, applies any promotion, takes payment and issues the ticket.</t>
         </is>
       </c>
     </row>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Add Promotion</t>
+          <t>Sell Snack</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Update Promotion</t>
+          <t>Add Promotion</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Delete Promotion</t>
+          <t>Update Promotion</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Search Promotion by Code, Period</t>
+          <t>Delete Promotion</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Post Showtime</t>
+          <t>Search Promotion by Code, Period</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Unpost Showtime</t>
+          <t>Post Showtime</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Select Seat</t>
+          <t>Unpost Showtime</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Apply Promotion to Booking</t>
+          <t>Select Seat</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Generate Ticket</t>
+          <t>Apply Promotion to Booking</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Validate Ticket at Entrance</t>
+          <t>Generate Ticket</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Issue Refund</t>
+          <t>Validate Ticket at Entrance</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Generate Sales Report</t>
+          <t>Issue Refund</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Cashier</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Generate Hall Occupancy Report</t>
+          <t>Generate Sales Report</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Manage User Roles</t>
+          <t>Generate Hall Occupancy Report</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Manage User Roles</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Cashier</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1344,10 +1344,25 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
           <t>Logout</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -1485,7 +1500,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>UC-50  —  Validate Ticket at Entrance</t>
+          <t>UC-51  —  Validate Ticket at Entrance</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -1498,7 +1513,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>UC-50</t>
+          <t>UC-51</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1608,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>UC-52  —  Generate Sales Report</t>
+          <t>UC-53  —  Generate Sales Report</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1606,7 +1621,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>UC-52</t>
+          <t>UC-53</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1828,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Replicate the CRUD template for every Add/Update/Delete/Search use case of Movie, Genre, Hall, Showtime, Customer, Staff, Booking, Ticket, Payment, Snack, Promotion. Write full specs for Post/Unpost Showtime, Select Seat, Apply Promotion, Add Payment, Generate Ticket, Issue Refund, the two reports, Manage User Roles, Login, Logout.</t>
+          <t>Replicate the CRUD template for every Add/Update/Delete/Search use case of Movie, Genre, Hall, Showtime, Customer, Staff, Booking, Ticket, Payment, Snack, Promotion. Write full specs for Post/Unpost Showtime, Select Seat, Apply Promotion, Add Payment, Generate Ticket, Sell Snack, Issue Refund, the two reports, Manage User Roles, Login, Logout.</t>
         </is>
       </c>
     </row>

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,10 +38,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="5">
@@ -104,13 +100,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -486,7 +480,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1382,463 +1376,6000 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>UC-25  —  Add Booking</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="n"/>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>UC-01  —  Add Movie</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Use Case ID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>UC-25</t>
+          <t>UC-01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Use Case Name</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Add Booking</t>
+          <t>Add Movie</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Actor(s)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new movie to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A new movie record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Movie form. 2. Enter the movie details. 3. Click Save. 4. The system validates the data and stores the new movie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>UC-02  —  Update Movie</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>UC-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Update Movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing movie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>The movie record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the movie. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>UC-03  —  Delete Movie</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>UC-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Delete Movie</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Removes a movie from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>The movie record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the movie. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>2a. The movie is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>UC-04  —  Search Movie by Title, Genre, Language</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>UC-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Search Movie by Title, Genre, Language</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>Cashier</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>The cashier creates a booking for a showtime on behalf of a customer: selects seats, applies any promotion, takes payment and issues the ticket.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Finds movie records by title, genre, language.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Cashier is logged in; a posted showtime with a free seat exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>A booking, ticket and payment are saved; the seats are marked sold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>1. Select a posted showtime. 2. Select seats (include Select Seat). 3. Enter/select the customer. 4. (optional) Apply a promotion (extend Apply Promotion). 5. Show total and take payment (include Add Payment). 6. Save booking and issue ticket (include Generate Ticket); mark seats sold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Title, Genre, Language). 2. The system displays the matching movie records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2a. Seat already sold -&gt; choose another seat. 5a. Payment fails -&gt; release seats, no ticket.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>UC-51  —  Validate Ticket at Entrance</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Use Case ID</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>UC-51</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Use Case Name</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Validate Ticket at Entrance</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Actor(s)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Cashier</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Checks a presented ticket is valid for the current showtime and marks it used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Cashier is logged in; the ticket exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Postconditions</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Ticket marked Used; entry granted or refused.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Main Flow</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>1. Scan/enter the ticket code. 2. Find ticket and showtime. 3. Check valid, right showtime, not used. 4. Mark Used and show 'Access granted' with the seat number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Alternative Flows</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>3a. Already used / wrong showtime -&gt; 'Invalid ticket', refuse entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>UC-53  —  Generate Sales Report</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Use Case ID</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>UC-53</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Use Case Name</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Generate Sales Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Actor(s)</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Produces a report of tickets sold and revenue for a chosen period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Manager is logged in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Postconditions</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>A report is displayed/printed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Main Flow</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>1. Choose the period (date range). 2. System totals tickets sold and revenue. 3. Display report with grand total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Alternative Flows</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>1a. No data in period -&gt; report shows zero totals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>UC-01  —  Add Movie</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Use Case ID</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>UC-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Use Case Name</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Add Movie</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Actor(s)</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Adds a new movie to the catalogue (template for all Add/Update/Delete/Search use cases).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Manager is logged in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Postconditions</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>A new movie record is stored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Main Flow</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>1. Open the Movie form. 2. Enter title, genre, duration, language, rating. 3. Save. 4. Validate and store.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Alternative Flows</t>
-        </is>
-      </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>3a. Duplicate / missing field -&gt; error, not saved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="3" t="n"/>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="3" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>UC-05  —  Add Genre</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Replicate the CRUD template for every Add/Update/Delete/Search use case of Movie, Genre, Hall, Showtime, Customer, Staff, Booking, Ticket, Payment, Snack, Promotion. Write full specs for Post/Unpost Showtime, Select Seat, Apply Promotion, Add Payment, Generate Ticket, Sell Snack, Issue Refund, the two reports, Manage User Roles, Login, Logout.</t>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>UC-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Add Genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new genre to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>A new genre record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Genre form. 2. Enter the genre details. 3. Click Save. 4. The system validates the data and stores the new genre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>UC-06  —  Update Genre</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>UC-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Update Genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing genre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>The genre record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the genre. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>UC-07  —  Delete Genre</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>UC-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Delete Genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Removes a genre from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>The genre record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the genre. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2a. The genre is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>UC-08  —  Search Genre by Name</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>UC-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Search Genre by Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Finds genre records by name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Name). 2. The system displays the matching genre records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>UC-09  —  Add Cinema Hall</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>UC-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Add Cinema Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new cinema hall to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>A new cinema hall record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Cinema Hall form. 2. Enter the cinema hall details. 3. Click Save. 4. The system validates the data and stores the new cinema hall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>UC-10  —  Update Cinema Hall</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>UC-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Update Cinema Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing cinema hall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>The cinema hall record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the cinema hall. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>UC-11  —  Delete Cinema Hall</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>UC-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Delete Cinema Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Removes a cinema hall from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>The cinema hall record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the cinema hall. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>2a. The cinema hall is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>UC-12  —  Search Cinema Hall by Name, Type, Capacity</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>UC-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Search Cinema Hall by Name, Type, Capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Finds cinema hall records by name, type, capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Name, Type, Capacity). 2. The system displays the matching cinema hall records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>UC-13  —  Add Showtime</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>UC-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Add Showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new showtime to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>A new showtime record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Showtime form. 2. Enter the showtime details. 3. Click Save. 4. The system validates the data and stores the new showtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>UC-14  —  Update Showtime</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>UC-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Update Showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing showtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>The showtime record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the showtime. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>UC-15  —  Delete Showtime</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>UC-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Delete Showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Removes a showtime from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>The showtime record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the showtime. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>2a. The showtime is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>UC-16  —  Search Showtime by Date, Movie, Hall, Time</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>UC-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Search Showtime by Date, Movie, Hall, Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Finds showtime records by date, movie, hall, time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Date, Movie, Hall, Time). 2. The system displays the matching showtime records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>UC-17  —  Add Customer</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>UC-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Add Customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new customer to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>A new customer record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Customer form. 2. Enter the customer details. 3. Click Save. 4. The system validates the data and stores the new customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>UC-18  —  Update Customer</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>UC-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Update Customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>The customer record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the customer. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>UC-19  —  Delete Customer</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>UC-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Delete Customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Removes a customer from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>The customer record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the customer. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>2a. The customer is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>UC-20  —  Search Customer by Id, Name, Phone</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>UC-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Search Customer by Id, Name, Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Finds customer records by id, name, phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Id, Name, Phone). 2. The system displays the matching customer records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>UC-21  —  Add Staff</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>UC-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Add Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new staff to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>A new staff record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Staff form. 2. Enter the staff details. 3. Click Save. 4. The system validates the data and stores the new staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>UC-22  —  Update Staff</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>UC-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Update Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>The staff record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the staff. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>UC-23  —  Delete Staff</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>UC-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Delete Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>Removes a staff from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>The staff record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the staff. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>2a. The staff is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>UC-24  —  Search Staff by Id, Name, Role</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>UC-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Search Staff by Id, Name, Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Finds staff records by id, name, role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Id, Name, Role). 2. The system displays the matching staff records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>UC-25  —  Add Booking</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>UC-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Add Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>The cashier creates a booking for a showtime on behalf of a customer: selects seats, applies any promotion, takes payment and issues the ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>The cashier is logged in; a posted showtime with a free seat exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>A booking, ticket and payment are saved; the seats are marked sold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>1. Select a posted showtime. 2. Select one or more seats («include» Select Seat). 3. Enter/select the customer. 4. (optional) Apply a promotion («extend» Apply Promotion). 5. Take payment («include» Add Payment). 6. Save the booking and issue the ticket («include» Generate Ticket); mark the seats sold. 7. Print/show the ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>2a. Seat already sold → choose another seat. 5a. Payment fails → release the seats, no ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>UC-26  —  Update Booking</t>
+        </is>
+      </c>
+      <c r="B251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>UC-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Update Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>The booking record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the booking. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>UC-27  —  Delete Booking</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>UC-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Delete Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>Removes a booking from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>The booking record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the booking. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>2a. The booking is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>UC-28  —  Search Booking by Id, Customer, Date, Showtime</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>UC-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Search Booking by Id, Customer, Date, Showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>Finds booking records by id, customer, date, showtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Id, Customer, Date, Showtime). 2. The system displays the matching booking records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>UC-29  —  Add Ticket</t>
+        </is>
+      </c>
+      <c r="B281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>UC-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>Add Ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new ticket to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>A new ticket record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Ticket form. 2. Enter the ticket details. 3. Click Save. 4. The system validates the data and stores the new ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>UC-30  —  Update Ticket</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>UC-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>Update Ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>The ticket record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the ticket. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>UC-31  —  Delete Ticket</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>UC-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Delete Ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>Removes a ticket from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>The ticket record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the ticket. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>2a. The ticket is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>UC-32  —  Search Ticket by Code, Showtime, Customer</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>UC-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>Search Ticket by Code, Showtime, Customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>Finds ticket records by code, showtime, customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Code, Showtime, Customer). 2. The system displays the matching ticket records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>UC-33  —  Add Payment</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>UC-33</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>Add Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>Charges the customer for a booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>A booking with a total amount is awaiting payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>A payment record is created (Paid or Failed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>1. Show the amount due and methods (Card, Mobile, Cash). 2. Choose a method. 3. Process payment, record as Paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>3a. Declined → record Failed; booking stays unpaid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>UC-34  —  Update Payment</t>
+        </is>
+      </c>
+      <c r="B331" s="5" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>UC-34</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Update Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>The payment record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the payment. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>UC-35  —  Delete Payment</t>
+        </is>
+      </c>
+      <c r="B341" s="5" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>UC-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>Delete Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>Removes a payment from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>The payment record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the payment. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>2a. The payment is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="inlineStr">
+        <is>
+          <t>UC-36  —  Search Payment by Id, Date, Method, Customer</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>UC-36</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>Search Payment by Id, Date, Method, Customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>Finds payment records by id, date, method, customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Id, Date, Method, Customer). 2. The system displays the matching payment records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="inlineStr">
+        <is>
+          <t>UC-37  —  Add Snack</t>
+        </is>
+      </c>
+      <c r="B361" s="5" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>UC-37</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>Add Snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new snack to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>A new snack record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Snack form. 2. Enter the snack details. 3. Click Save. 4. The system validates the data and stores the new snack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="4" t="inlineStr">
+        <is>
+          <t>UC-38  —  Update Snack</t>
+        </is>
+      </c>
+      <c r="B371" s="5" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>UC-38</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>Update Snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing snack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>The snack record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the snack. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="4" t="inlineStr">
+        <is>
+          <t>UC-39  —  Delete Snack</t>
+        </is>
+      </c>
+      <c r="B381" s="5" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>UC-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>Delete Snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>Removes a snack from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>The snack record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the snack. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>2a. The snack is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="4" t="inlineStr">
+        <is>
+          <t>UC-40  —  Search Snack by Name, Category</t>
+        </is>
+      </c>
+      <c r="B391" s="5" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>UC-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>Search Snack by Name, Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>Finds snack records by name, category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Name, Category). 2. The system displays the matching snack records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="4" t="inlineStr">
+        <is>
+          <t>UC-41  —  Sell Snack</t>
+        </is>
+      </c>
+      <c r="B401" s="5" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>UC-41</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>Sell Snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>Sells one or more snacks to a customer and records the snack order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>The cashier is logged in; snacks exist in the menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>A snack order is saved with its line(s) and total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the snack(s) and quantity. 2. The system computes the total. 3. Take payment. 4. Save the snack order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>2a. Snack out of stock → choose another.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="4" t="inlineStr">
+        <is>
+          <t>UC-42  —  Add Promotion</t>
+        </is>
+      </c>
+      <c r="B411" s="5" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>UC-42</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>Add Promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>Adds a new promotion to the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="inlineStr">
+        <is>
+          <t>A new promotion record is stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>1. Open the Promotion form. 2. Enter the promotion details. 3. Click Save. 4. The system validates the data and stores the new promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B419" s="3" t="inlineStr">
+        <is>
+          <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="4" t="inlineStr">
+        <is>
+          <t>UC-43  —  Update Promotion</t>
+        </is>
+      </c>
+      <c r="B421" s="5" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>UC-43</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="inlineStr">
+        <is>
+          <t>Update Promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>Modifies the details of an existing promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
+          <t>The promotion record is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>1. Search and select the promotion. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>3a. Invalid data → error, no change is saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="4" t="inlineStr">
+        <is>
+          <t>UC-44  —  Delete Promotion</t>
+        </is>
+      </c>
+      <c r="B431" s="5" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>UC-44</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>Delete Promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>Removes a promotion from the system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>The Manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B437" s="3" t="inlineStr">
+        <is>
+          <t>The promotion record is deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the promotion. 2. Confirm the deletion. 3. The system removes the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
+        <is>
+          <t>2a. The promotion is referenced elsewhere → the deletion is blocked with a warning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="4" t="inlineStr">
+        <is>
+          <t>UC-45  —  Search Promotion by Code, Period</t>
+        </is>
+      </c>
+      <c r="B441" s="5" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>UC-45</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>Search Promotion by Code, Period</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>Finds promotion records by code, period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>The Cashier is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>The matching records are displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the search criteria (Code, Period). 2. The system displays the matching promotion records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>2a. No match → the system shows an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="4" t="inlineStr">
+        <is>
+          <t>UC-46  —  Post Showtime</t>
+        </is>
+      </c>
+      <c r="B451" s="5" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>UC-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B453" s="3" t="inlineStr">
+        <is>
+          <t>Post Showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B455" s="3" t="inlineStr">
+        <is>
+          <t>Publishes a showtime so it becomes available for selling tickets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>The manager is logged in; the showtime exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B457" s="3" t="inlineStr">
+        <is>
+          <t>The showtime status becomes Posted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the showtime. 2. Click Post. 3. The status becomes Posted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B459" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="4" t="inlineStr">
+        <is>
+          <t>UC-47  —  Unpost Showtime</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>UC-47</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B463" s="3" t="inlineStr">
+        <is>
+          <t>Unpost Showtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
+        <is>
+          <t>Hides a showtime so tickets can no longer be sold for it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>The manager is logged in; the showtime is Posted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B467" s="3" t="inlineStr">
+        <is>
+          <t>The showtime status becomes Unposted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the showtime. 2. Click Unpost. 3. The status becomes Unposted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>2a. Tickets already sold → warn before unposting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="4" t="inlineStr">
+        <is>
+          <t>UC-48  —  Select Seat</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>UC-48</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B473" s="3" t="inlineStr">
+        <is>
+          <t>Select Seat</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B475" s="3" t="inlineStr">
+        <is>
+          <t>Chooses one or more available seats for a showtime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>A showtime is selected; a seat map is displayed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B477" s="3" t="inlineStr">
+        <is>
+          <t>The chosen seats are reserved for the booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>1. The system shows available seats. 2. The cashier selects the seat(s). 3. The seats are held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>2a. Seat just taken → ask for another seat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="4" t="inlineStr">
+        <is>
+          <t>UC-49  —  Apply Promotion to Booking</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>UC-49</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>Apply Promotion to Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B485" s="3" t="inlineStr">
+        <is>
+          <t>Applies a valid promotion code to a booking to reduce the total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>A booking is in progress; a valid promotion exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>The discount is applied and the total recalculated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter the promotion code. 2. The system checks it is valid and in date. 3. Apply the discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>2a. Invalid/expired code → no discount; show a message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="4" t="inlineStr">
+        <is>
+          <t>UC-50  —  Generate Ticket</t>
+        </is>
+      </c>
+      <c r="B491" s="5" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>UC-50</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>Generate Ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>Issues the ticket(s) for a paid booking with a unique code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>The booking is paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>Ticket(s) are created with status Valid and printed/shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>1. Create a ticket per seat with a unique code. 2. Print/show the ticket(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="inlineStr">
+        <is>
+          <t>UC-51  —  Validate Ticket at Entrance</t>
+        </is>
+      </c>
+      <c r="B501" s="5" t="n"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>UC-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>Validate Ticket at Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>Checks that a presented ticket is valid for the current showtime and marks it used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>The cashier is logged in; the ticket exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B507" s="3" t="inlineStr">
+        <is>
+          <t>The ticket is marked Used; entry granted or refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>1. Scan/enter the ticket code. 2. Find the ticket and showtime. 3. Check it is Valid, for the right showtime and not used. 4. Mark Used and show 'Access granted' with the seat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>3a. Already used / wrong showtime → 'Invalid ticket', refuse entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="4" t="inlineStr">
+        <is>
+          <t>UC-52  —  Issue Refund</t>
+        </is>
+      </c>
+      <c r="B511" s="5" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>UC-52</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>Issue Refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>Refunds a cancelled booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>The booking is paid and being cancelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>A refund payment is recorded; the ticket status becomes Refunded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the cancelled booking. 2. Confirm the refund. 3. Record the refund and mark the ticket Refunded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="inlineStr">
+        <is>
+          <t>2a. Booking not paid → nothing to refund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="4" t="inlineStr">
+        <is>
+          <t>UC-53  —  Generate Sales Report</t>
+        </is>
+      </c>
+      <c r="B521" s="5" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>UC-53</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>Generate Sales Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>Produces a report of tickets sold and revenue for a chosen period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>The manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>A report is displayed/printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>1. Choose the period. 2. The system totals tickets sold and revenue. 3. Display the report with a grand total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>1a. No data → zero totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="4" t="inlineStr">
+        <is>
+          <t>UC-54  —  Generate Hall Occupancy Report</t>
+        </is>
+      </c>
+      <c r="B531" s="5" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>UC-54</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>Generate Hall Occupancy Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>Shows, per showtime, the seats sold versus capacity and the occupancy rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>The manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>An occupancy report is displayed/printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B538" s="3" t="inlineStr">
+        <is>
+          <t>1. Choose the period/hall. 2. The system computes seats sold / capacity per showtime. 3. Display the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B539" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="4" t="inlineStr">
+        <is>
+          <t>UC-55  —  Manage User Roles</t>
+        </is>
+      </c>
+      <c r="B541" s="5" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>UC-55</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B543" s="3" t="inlineStr">
+        <is>
+          <t>Manage User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B545" s="3" t="inlineStr">
+        <is>
+          <t>Assigns or changes the role (Manager/Cashier) of a staff account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>The manager is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B547" s="3" t="inlineStr">
+        <is>
+          <t>The staff member's role is updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>1. Select the staff account. 2. Choose the role. 3. Save.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B549" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="inlineStr">
+        <is>
+          <t>UC-56  —  Login</t>
+        </is>
+      </c>
+      <c r="B551" s="5" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B552" s="3" t="inlineStr">
+        <is>
+          <t>UC-56</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B554" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B555" s="3" t="inlineStr">
+        <is>
+          <t>Authenticates a staff member and opens the menu according to their role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B556" s="3" t="inlineStr">
+        <is>
+          <t>The application is running; a valid staff account exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B557" s="3" t="inlineStr">
+        <is>
+          <t>The staff member is authenticated with role-based access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B558" s="3" t="inlineStr">
+        <is>
+          <t>1. Enter username and password. 2. The system validates and reads the role. 3. Open the menu (full for Manager, selling for Cashier).</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>2a. Invalid credentials → show 'Invalid login credentials', stay on the login screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="inlineStr">
+        <is>
+          <t>UC-57  —  Logout</t>
+        </is>
+      </c>
+      <c r="B561" s="5" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="6" t="inlineStr">
+        <is>
+          <t>Use Case ID</t>
+        </is>
+      </c>
+      <c r="B562" s="3" t="inlineStr">
+        <is>
+          <t>UC-57</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="6" t="inlineStr">
+        <is>
+          <t>Use Case Name</t>
+        </is>
+      </c>
+      <c r="B563" s="3" t="inlineStr">
+        <is>
+          <t>Logout</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="6" t="inlineStr">
+        <is>
+          <t>Actor(s)</t>
+        </is>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>Cashier</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B565" s="3" t="inlineStr">
+        <is>
+          <t>Ends the staff member's session securely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="6" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>A staff member is logged in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="6" t="inlineStr">
+        <is>
+          <t>Postconditions</t>
+        </is>
+      </c>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>The session is closed; the login screen is shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="6" t="inlineStr">
+        <is>
+          <t>Main Flow</t>
+        </is>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>1. Click Logout. 2. The system closes the session and returns to the login screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="6" t="inlineStr">
+        <is>
+          <t>Alternative Flows</t>
+        </is>
+      </c>
+      <c r="B569" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="57">
+    <mergeCell ref="A521:B521"/>
+    <mergeCell ref="A441:B441"/>
+    <mergeCell ref="A201:B201"/>
+    <mergeCell ref="A421:B421"/>
+    <mergeCell ref="A431:B431"/>
+    <mergeCell ref="A191:B191"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A511:B511"/>
+    <mergeCell ref="A291:B291"/>
+    <mergeCell ref="A281:B281"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A561:B561"/>
+    <mergeCell ref="A241:B241"/>
+    <mergeCell ref="A461:B461"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A551:B551"/>
+    <mergeCell ref="A271:B271"/>
+    <mergeCell ref="A221:B221"/>
+    <mergeCell ref="A501:B501"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A531:B531"/>
+    <mergeCell ref="A471:B471"/>
+    <mergeCell ref="A351:B351"/>
+    <mergeCell ref="A301:B301"/>
+    <mergeCell ref="A341:B341"/>
+    <mergeCell ref="A101:B101"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A381:B381"/>
+    <mergeCell ref="A251:B251"/>
+    <mergeCell ref="A151:B151"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A331:B331"/>
+    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="A361:B361"/>
+    <mergeCell ref="A181:B181"/>
+    <mergeCell ref="A321:B321"/>
+    <mergeCell ref="A311:B311"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A231:B231"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A371:B371"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A411:B411"/>
+    <mergeCell ref="A451:B451"/>
+    <mergeCell ref="A491:B491"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A481:B481"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="A401:B401"/>
+    <mergeCell ref="A541:B541"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A391:B391"/>
+    <mergeCell ref="A211:B211"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A261:B261"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1854,8 +7385,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -7421,7 +7421,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>INT (auto)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -7477,10 +7477,14 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>ENUM('MANAGER','CASHIER')</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr"/>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Manager / Cashier</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -7928,10 +7932,14 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>ENUM('Posted','Unposted')</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr"/>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Posted / Unposted</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -8046,10 +8054,14 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>ENUM('Confirmed','Cancelled')</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr"/>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Confirmed / Cancelled</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -8156,10 +8168,14 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>ENUM('Valid','Used','Refunded')</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr"/>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Valid / Used / Refunded</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -8240,10 +8256,14 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>ENUM('Card','Mobile','Cash')</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr"/>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Card / Mobile / Cash</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
@@ -8266,10 +8286,14 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>ENUM('Paid','Refunded')</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr"/>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Paid / Refunded</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">

--- a/cinema-management-system-analysis/Cinema_Management_System.xlsx
+++ b/cinema-management-system-analysis/Cinema_Management_System.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,10 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,7 +71,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -89,11 +93,25 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -107,15 +125,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1411,7 +1432,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>UC-01</t>
         </is>
@@ -1423,7 +1444,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Add Movie</t>
         </is>
@@ -1435,7 +1456,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -1447,7 +1468,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Adds a new movie to the system.</t>
         </is>
@@ -1459,7 +1480,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>The Manager is logged in.</t>
         </is>
@@ -1471,7 +1492,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>A new movie record is stored.</t>
         </is>
@@ -1483,7 +1504,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>1. Open the Movie form. 2. Enter the movie details. 3. Click Save. 4. The system validates the data and stores the new movie.</t>
         </is>
@@ -1495,7 +1516,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>3a. A required field is missing or a duplicate exists → the system shows an error and nothing is saved.</t>
         </is>
@@ -1515,7 +1536,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>UC-02</t>
         </is>
@@ -1527,7 +1548,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Update Movie</t>
         </is>
@@ -1539,7 +1560,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -1551,7 +1572,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Modifies the details of an existing movie.</t>
         </is>
@@ -1563,7 +1584,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>The Manager is logged in.</t>
         </is>
@@ -1575,7 +1596,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>The movie record is updated.</t>
         </is>
@@ -1587,7 +1608,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>1. Search and select the movie. 2. Edit the details. 3. Click Save. 4. The system validates and updates the record.</t>
         </is>
@@ -1599,7 +1620,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>3a. Invalid data → error, no change is saved.</t>
         </is>
@@ -1619,7 +1640,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>UC-03</t>
         </is>
@@ -1631,7 +1652,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Delete Movie</t>
         </is>
@@ -1643,7 +1664,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -1655,7 +1676,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Removes a movie from the system.</t>
         </is>
@@ -1667,7 +1688,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>The Manager is logged in.</t>
         </is>
@@ -1679,7 +1700,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>The movie record is deleted.</t>
         </is>
@@ -1691,7 +1712,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>1. Select the movie. 2. Confirm the deletion. 3. The system removes the record.</t>
         </is>
@@ -1703,7 +1724,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>2a. The movie is referenced elsewhere → the deletion is blocked with a warning.</t>
         </is>
@@ -1723,7 +1744,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>UC-04</t>
         </is>
@@ -1735,7 +1756,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Search Movie by Title, Genre, Language</t>
         </is>
@@ -1747,7 +1768,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -1759,7 +1780,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Finds movie records by title, genre, language.</t>
         </is>
@@ -1771,7 +1792,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>The Cashier is logged in.</t>
         </is>
@@ -1783,7 +1804,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>The matching records are displayed.</t>
         </is>
@@ -1795,7 +1816,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>1. Enter the search criteria (Title, Genre, Language). 2. The system displays the matching movie records.</t>
         </is>
@@ -1807,7 +1828,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>2a. No match → the system shows an empty result.</t>
         </is>
@@ -1827,7 +1848,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>UC-25</t>
         </is>
@@ -1839,7 +1860,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Add Booking</t>
         </is>
@@ -1851,7 +1872,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -1863,7 +1884,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>The cashier creates a booking for a showtime on behalf of a customer: selects seats, applies any promotion, takes payment and issues the ticket.</t>
         </is>
@@ -1875,7 +1896,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>The cashier is logged in; a posted showtime with a free seat exists.</t>
         </is>
@@ -1887,7 +1908,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>A booking, ticket and payment are saved; the seats are marked sold.</t>
         </is>
@@ -1899,7 +1920,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>1. Select a posted showtime. 2. Select one or more seats («include» Select Seat). 3. Enter/select the customer. 4. (optional) Apply a promotion («extend» Apply Promotion). 5. Take payment («include» Add Payment). 6. Save the booking and issue the ticket («include» Generate Ticket); mark the seats sold. 7. Print/show the ticket.</t>
         </is>
@@ -1911,7 +1932,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>2a. Seat already sold → choose another seat. 5a. Payment fails → release the seats, no ticket.</t>
         </is>
@@ -1931,7 +1952,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>UC-48</t>
         </is>
@@ -1943,7 +1964,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Select Seat</t>
         </is>
@@ -1955,7 +1976,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -1967,7 +1988,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Chooses one or more available seats for a showtime.</t>
         </is>
@@ -1979,7 +2000,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>A showtime is selected; a seat map is displayed.</t>
         </is>
@@ -1991,7 +2012,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>The chosen seats are reserved for the booking.</t>
         </is>
@@ -2003,7 +2024,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>1. The system shows available seats. 2. The cashier selects the seat(s). 3. The seats are held.</t>
         </is>
@@ -2015,7 +2036,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>2a. Seat just taken → ask for another seat.</t>
         </is>
@@ -2035,7 +2056,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>UC-33</t>
         </is>
@@ -2047,7 +2068,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Add Payment</t>
         </is>
@@ -2059,7 +2080,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -2071,7 +2092,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Charges the customer for a booking.</t>
         </is>
@@ -2083,7 +2104,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>A booking with a total amount is awaiting payment.</t>
         </is>
@@ -2095,7 +2116,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>A payment record is created (Paid or Failed).</t>
         </is>
@@ -2107,7 +2128,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>1. Show the amount due and methods (Card, Mobile, Cash). 2. Choose a method. 3. Process payment, record as Paid.</t>
         </is>
@@ -2119,7 +2140,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>3a. Declined → record Failed; booking stays unpaid.</t>
         </is>
@@ -2139,7 +2160,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>UC-50</t>
         </is>
@@ -2151,7 +2172,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Generate Ticket</t>
         </is>
@@ -2163,7 +2184,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -2175,7 +2196,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Issues the ticket(s) for a paid booking with a unique code.</t>
         </is>
@@ -2187,7 +2208,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>The booking is paid.</t>
         </is>
@@ -2199,7 +2220,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Ticket(s) are created with status Valid and printed/shown.</t>
         </is>
@@ -2211,7 +2232,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>1. Create a ticket per seat with a unique code. 2. Print/show the ticket(s).</t>
         </is>
@@ -2223,7 +2244,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2243,7 +2264,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>UC-49</t>
         </is>
@@ -2255,7 +2276,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Apply Promotion to Booking</t>
         </is>
@@ -2267,7 +2288,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -2279,7 +2300,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Applies a valid promotion code to a booking to reduce the total.</t>
         </is>
@@ -2291,7 +2312,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>A booking is in progress; a valid promotion exists.</t>
         </is>
@@ -2303,7 +2324,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>The discount is applied and the total recalculated.</t>
         </is>
@@ -2315,7 +2336,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>1. Enter the promotion code. 2. The system checks it is valid and in date. 3. Apply the discount.</t>
         </is>
@@ -2327,7 +2348,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>2a. Invalid/expired code → no discount; show a message.</t>
         </is>
@@ -2347,7 +2368,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>UC-52</t>
         </is>
@@ -2359,7 +2380,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Issue Refund</t>
         </is>
@@ -2371,7 +2392,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -2383,7 +2404,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>Refunds a cancelled booking.</t>
         </is>
@@ -2395,7 +2416,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>The booking is paid and being cancelled.</t>
         </is>
@@ -2407,7 +2428,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>A refund payment is recorded; the ticket status becomes Refunded.</t>
         </is>
@@ -2419,7 +2440,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>1. Select the cancelled booking. 2. Confirm the refund. 3. Record the refund and mark the ticket Refunded.</t>
         </is>
@@ -2431,7 +2452,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>2a. Booking not paid → nothing to refund.</t>
         </is>
@@ -2451,7 +2472,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>UC-51</t>
         </is>
@@ -2463,7 +2484,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>Validate Ticket at Entrance</t>
         </is>
@@ -2475,7 +2496,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -2487,7 +2508,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>Checks that a presented ticket is valid for the current showtime and marks it used.</t>
         </is>
@@ -2499,7 +2520,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>The cashier is logged in; the ticket exists.</t>
         </is>
@@ -2511,7 +2532,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>The ticket is marked Used; entry granted or refused.</t>
         </is>
@@ -2523,7 +2544,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>1. Scan/enter the ticket code. 2. Find the ticket and showtime. 3. Check it is Valid, for the right showtime and not used. 4. Mark Used and show 'Access granted' with the seat.</t>
         </is>
@@ -2535,7 +2556,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>3a. Already used / wrong showtime → 'Invalid ticket', refuse entry.</t>
         </is>
@@ -2555,7 +2576,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>UC-41</t>
         </is>
@@ -2567,7 +2588,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>Sell Snack</t>
         </is>
@@ -2579,7 +2600,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -2591,7 +2612,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>Sells one or more snacks to a customer and records the snack order.</t>
         </is>
@@ -2603,7 +2624,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>The cashier is logged in; snacks exist in the menu.</t>
         </is>
@@ -2615,7 +2636,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>A snack order is saved with its line(s) and total.</t>
         </is>
@@ -2627,7 +2648,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>1. Select the snack(s) and quantity. 2. The system computes the total. 3. Take payment. 4. Save the snack order.</t>
         </is>
@@ -2639,7 +2660,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>2a. Snack out of stock → choose another.</t>
         </is>
@@ -2659,7 +2680,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>UC-46</t>
         </is>
@@ -2671,7 +2692,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>Post Showtime</t>
         </is>
@@ -2683,7 +2704,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -2695,7 +2716,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>Publishes a showtime so it becomes available for selling tickets.</t>
         </is>
@@ -2707,7 +2728,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>The manager is logged in; the showtime exists.</t>
         </is>
@@ -2719,7 +2740,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>The showtime status becomes Posted.</t>
         </is>
@@ -2731,7 +2752,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>1. Select the showtime. 2. Click Post. 3. The status becomes Posted.</t>
         </is>
@@ -2743,7 +2764,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2763,7 +2784,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>UC-47</t>
         </is>
@@ -2775,7 +2796,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>Unpost Showtime</t>
         </is>
@@ -2787,7 +2808,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -2799,7 +2820,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>Hides a showtime so tickets can no longer be sold for it.</t>
         </is>
@@ -2811,7 +2832,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>The manager is logged in; the showtime is Posted.</t>
         </is>
@@ -2823,7 +2844,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>The showtime status becomes Unposted.</t>
         </is>
@@ -2835,7 +2856,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>1. Select the showtime. 2. Click Unpost. 3. The status becomes Unposted.</t>
         </is>
@@ -2847,7 +2868,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>2a. Tickets already sold → warn before unposting.</t>
         </is>
@@ -2867,7 +2888,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>UC-53</t>
         </is>
@@ -2879,7 +2900,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B145" s="3" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>Generate Sales Report</t>
         </is>
@@ -2891,7 +2912,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -2903,7 +2924,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>Produces a report of tickets sold and revenue for a chosen period.</t>
         </is>
@@ -2915,7 +2936,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>The manager is logged in.</t>
         </is>
@@ -2927,7 +2948,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>A report is displayed/printed.</t>
         </is>
@@ -2939,7 +2960,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>1. Choose the period. 2. The system totals tickets sold and revenue. 3. Display the report with a grand total.</t>
         </is>
@@ -2951,7 +2972,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>1a. No data → zero totals.</t>
         </is>
@@ -2971,7 +2992,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>UC-54</t>
         </is>
@@ -2983,7 +3004,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>Generate Hall Occupancy Report</t>
         </is>
@@ -2995,7 +3016,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -3007,7 +3028,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>Shows, per showtime, the seats sold versus capacity and the occupancy rate.</t>
         </is>
@@ -3019,7 +3040,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>The manager is logged in.</t>
         </is>
@@ -3031,7 +3052,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>An occupancy report is displayed/printed.</t>
         </is>
@@ -3043,7 +3064,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>1. Choose the period/hall. 2. The system computes seats sold / capacity per showtime. 3. Display the report.</t>
         </is>
@@ -3055,7 +3076,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3075,7 +3096,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>UC-55</t>
         </is>
@@ -3087,7 +3108,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>Manage User Roles</t>
         </is>
@@ -3099,7 +3120,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
@@ -3111,7 +3132,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>Assigns or changes the role (Manager/Cashier) of a staff account.</t>
         </is>
@@ -3123,7 +3144,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>The manager is logged in.</t>
         </is>
@@ -3135,7 +3156,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>The staff member's role is updated.</t>
         </is>
@@ -3147,7 +3168,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>1. Select the staff account. 2. Choose the role. 3. Save.</t>
         </is>
@@ -3159,7 +3180,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3179,7 +3200,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>UC-56</t>
         </is>
@@ -3191,7 +3212,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
@@ -3203,7 +3224,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -3215,7 +3236,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>Authenticates a staff member and opens the menu according to their role.</t>
         </is>
@@ -3227,7 +3248,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>The application is running; a valid staff account exists.</t>
         </is>
@@ -3239,7 +3260,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>The staff member is authenticated with role-based access.</t>
         </is>
@@ -3251,7 +3272,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>1. Enter username and password. 2. The system validates and reads the role. 3. Open the menu (full for Manager, selling for Cashier).</t>
         </is>
@@ -3263,7 +3284,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>2a. Invalid credentials → show 'Invalid login credentials', stay on the login screen.</t>
         </is>
@@ -3283,7 +3304,7 @@
           <t>Use Case ID</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>UC-57</t>
         </is>
@@ -3295,7 +3316,7 @@
           <t>Use Case Name</t>
         </is>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>Logout</t>
         </is>
@@ -3307,7 +3328,7 @@
           <t>Actor(s)</t>
         </is>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>Cashier</t>
         </is>
@@ -3319,7 +3340,7 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B187" s="3" t="inlineStr">
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>Ends the staff member's session securely.</t>
         </is>
@@ -3331,7 +3352,7 @@
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>A staff member is logged in.</t>
         </is>
@@ -3343,7 +3364,7 @@
           <t>Postconditions</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>The session is closed; the login screen is shown.</t>
         </is>
@@ -3355,7 +3376,7 @@
           <t>Main Flow</t>
         </is>
       </c>
-      <c r="B190" s="3" t="inlineStr">
+      <c r="B190" s="8" t="inlineStr">
         <is>
           <t>1. Click Logout. 2. The system closes the session and returns to the login screen.</t>
         </is>
@@ -3367,7 +3388,7 @@
           <t>Alternative Flows</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3415,1197 +3436,1197 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>staff</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>staff_id</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr"/>
+      <c r="C4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr"/>
+      <c r="C5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(255)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Manager / Cashier</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>customer</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr"/>
+      <c r="C12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(20)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr"/>
+      <c r="C14" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>genre</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>genre_id</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr"/>
+      <c r="C19" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>movie</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>movie_id</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(120)</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr"/>
+      <c r="C24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>genre_id</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; genre</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr"/>
+      <c r="C26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(40)</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr"/>
+      <c r="C27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr"/>
+      <c r="C28" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>cinema_hall</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>hall_id</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>hall_name</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(60)</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr"/>
+      <c r="C33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>hall_type</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(20)</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr"/>
+      <c r="C34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr"/>
+      <c r="C35" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>showtime</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>show_id</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>movie_id</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; movie</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>hall_id</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; cinema_hall</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>show_date</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr"/>
+      <c r="C42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>show_time</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr"/>
+      <c r="C43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>ticket_price</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr"/>
+      <c r="C44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Posted / Unposted</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>booking</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>booking_id</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; customer</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>show_id</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; showtime</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>promotion_id</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; promotion (null)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>booking_datetime</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr"/>
+      <c r="C53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Confirmed / Cancelled</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>total_amount</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr"/>
+      <c r="C55" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>ticket</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>ticket_id</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>booking_id</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; booking</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>seat_number</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(8)</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr"/>
+      <c r="C61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr"/>
+      <c r="C62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>Valid / Used / Refunded</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>payment</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>payment_id</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>booking_id</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; booking</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr"/>
+      <c r="C69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>Card / Mobile / Cash</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>payment_datetime</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr"/>
+      <c r="C71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(10)</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>Paid / Refunded</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>snack</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>snack_id</t>
         </is>
       </c>
-      <c r="B76" s="10" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr"/>
+      <c r="C77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(30)</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr"/>
+      <c r="C78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr"/>
+      <c r="C79" s="11" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>snack_order</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>booking_id</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; booking</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>snack_id</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>FK -&gt; snack</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr"/>
+      <c r="C86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>line_total</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>DECIMAL(8,2)</t>
         </is>
       </c>
-      <c r="C87" s="10" t="inlineStr"/>
+      <c r="C87" s="11" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>promotion</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t>promotion_id</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(20)</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr"/>
+      <c r="C92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>discount_percent</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>DECIMAL(5,2)</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr"/>
+      <c r="C94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr"/>
+      <c r="C95" s="11" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr"/>
+      <c r="C96" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
